--- a/cvnain/data/cv_data.xlsx
+++ b/cvnain/data/cv_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abc\Desktop\academic-website\cvnain\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327D9234-84EF-422A-A896-ED0012D6FA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CCD44C-0A3B-4836-B553-D38B4F1BA288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="437">
   <si>
     <t>category</t>
   </si>
@@ -1289,9 +1289,6 @@
     <t>software/splicer-app/index.html</t>
   </si>
   <si>
-    <t>software/app.R</t>
-  </si>
-  <si>
     <t>software/example_data.csv</t>
   </si>
   <si>
@@ -1334,9 +1331,6 @@
     <t>A Shiny app that joins series published at different base years (WPI, IIP, CPI, GDP/GVA old vs new series) into one continuous series. Three splicing methods: ratio splice at a link period, average-overlap ratio, and growth-rate retropolation, with optional rebasing, an interactive chart, a full results table, and CSV/Excel download.</t>
   </si>
   <si>
-    <t>No installation needed: the app runs entirely in your browser; the first load takes a little while. To run it locally instead, download the app. R and use shiny::runApp().</t>
-  </si>
-  <si>
     <t>A standing dashboard of Indian retail inflation, built straight from MoSPI’s open API: headline CPI trend against the RBI’s tolerance band, the rural–urban gap, inflation by spending division, each division’s contribution to the headline rate, a state-wise map, and a 2012-base historical view. The 2012- and 2024-base series are chain-linked, with the switch marked on the chart.</t>
   </si>
   <si>
@@ -1347,6 +1341,9 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No installation needed: the app runs entirely in your browser; the first load takes a little while. </t>
   </si>
 </sst>
 </file>
@@ -1940,7 +1937,7 @@
         <v>414</v>
       </c>
       <c r="H1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1951,48 +1948,45 @@
         <v>416</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E2" t="s">
         <v>417</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>418</v>
       </c>
-      <c r="G2" t="s">
-        <v>419</v>
-      </c>
       <c r="H2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B3" t="s">
         <v>422</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E3" t="s">
         <v>423</v>
       </c>
-      <c r="C3" t="s">
-        <v>434</v>
-      </c>
-      <c r="D3" t="s">
-        <v>435</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H3" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" t="s">
-        <v>421</v>
-      </c>
-      <c r="G3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H3" t="s">
-        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2086,7 @@
         <v>113</v>
       </c>
       <c r="D1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -2590,7 +2584,7 @@
         <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E19" t="s">
         <v>215</v>
@@ -2651,7 +2645,7 @@
         <v>2024</v>
       </c>
       <c r="D21" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E21" t="s">
         <v>227</v>
@@ -2927,7 +2921,7 @@
         <v>2026</v>
       </c>
       <c r="D30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>401</v>
@@ -2959,7 +2953,7 @@
         <v>2025</v>
       </c>
       <c r="D31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E31" t="s">
         <v>279</v>
@@ -2994,7 +2988,7 @@
         <v>2025</v>
       </c>
       <c r="D32" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E32" t="s">
         <v>282</v>
@@ -4051,10 +4045,10 @@
         <v>362</v>
       </c>
       <c r="B2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D2" t="s">
         <v>364</v>
@@ -4079,10 +4073,10 @@
         <v>362</v>
       </c>
       <c r="B4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C4" t="s">
         <v>426</v>
-      </c>
-      <c r="C4" t="s">
-        <v>427</v>
       </c>
       <c r="D4">
         <v>2026</v>
@@ -4093,13 +4087,13 @@
         <v>362</v>
       </c>
       <c r="B5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C5" t="s">
         <v>428</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>429</v>
-      </c>
-      <c r="D5" t="s">
-        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/cvnain/data/cv_data.xlsx
+++ b/cvnain/data/cv_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abc\Desktop\academic-website\cvnain\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CCD44C-0A3B-4836-B553-D38B4F1BA288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327D9234-84EF-422A-A896-ED0012D6FA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="438">
   <si>
     <t>category</t>
   </si>
@@ -1289,6 +1289,9 @@
     <t>software/splicer-app/index.html</t>
   </si>
   <si>
+    <t>software/app.R</t>
+  </si>
+  <si>
     <t>software/example_data.csv</t>
   </si>
   <si>
@@ -1331,6 +1334,9 @@
     <t>A Shiny app that joins series published at different base years (WPI, IIP, CPI, GDP/GVA old vs new series) into one continuous series. Three splicing methods: ratio splice at a link period, average-overlap ratio, and growth-rate retropolation, with optional rebasing, an interactive chart, a full results table, and CSV/Excel download.</t>
   </si>
   <si>
+    <t>No installation needed: the app runs entirely in your browser; the first load takes a little while. To run it locally instead, download the app. R and use shiny::runApp().</t>
+  </si>
+  <si>
     <t>A standing dashboard of Indian retail inflation, built straight from MoSPI’s open API: headline CPI trend against the RBI’s tolerance band, the rural–urban gap, inflation by spending division, each division’s contribution to the headline rate, a state-wise map, and a 2012-base historical view. The 2012- and 2024-base series are chain-linked, with the switch marked on the chart.</t>
   </si>
   <si>
@@ -1341,9 +1347,6 @@
   </si>
   <si>
     <t>YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No installation needed: the app runs entirely in your browser; the first load takes a little while. </t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1940,7 @@
         <v>414</v>
       </c>
       <c r="H1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1948,45 +1951,48 @@
         <v>416</v>
       </c>
       <c r="C2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E2" t="s">
         <v>417</v>
       </c>
+      <c r="F2" t="s">
+        <v>418</v>
+      </c>
       <c r="G2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F3" t="s">
         <v>421</v>
       </c>
-      <c r="B3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D3" t="s">
-        <v>433</v>
-      </c>
-      <c r="E3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" t="s">
-        <v>420</v>
-      </c>
       <c r="G3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2092,7 @@
         <v>113</v>
       </c>
       <c r="D1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -2584,7 +2590,7 @@
         <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
         <v>215</v>
@@ -2645,7 +2651,7 @@
         <v>2024</v>
       </c>
       <c r="D21" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E21" t="s">
         <v>227</v>
@@ -2921,7 +2927,7 @@
         <v>2026</v>
       </c>
       <c r="D30" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>401</v>
@@ -2953,7 +2959,7 @@
         <v>2025</v>
       </c>
       <c r="D31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E31" t="s">
         <v>279</v>
@@ -2988,7 +2994,7 @@
         <v>2025</v>
       </c>
       <c r="D32" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E32" t="s">
         <v>282</v>
@@ -4045,10 +4051,10 @@
         <v>362</v>
       </c>
       <c r="B2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D2" t="s">
         <v>364</v>
@@ -4073,10 +4079,10 @@
         <v>362</v>
       </c>
       <c r="B4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D4">
         <v>2026</v>
@@ -4087,13 +4093,13 @@
         <v>362</v>
       </c>
       <c r="B5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
